--- a/exams/noip_basic.xlsx
+++ b/exams/noip_basic.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="123" windowWidth="30561" windowHeight="17489" activeTab="1" tabRatio="600"/>
+    <workbookView xWindow="105" yWindow="108" windowWidth="30546" windowHeight="17473" activeTab="3" tabRatio="600"/>
   </bookViews>
   <sheets>
     <sheet name="ExamConfig" sheetId="1" r:id="rId1"/>
     <sheet name="SingleChoice" sheetId="2" r:id="rId2"/>
     <sheet name="FillBlank" sheetId="3" r:id="rId3"/>
-    <sheet name="Programming" sheetId="4" r:id="rId4"/>
+    <sheet name="TrueFalse" sheetId="5" r:id="rId4"/>
+    <sheet name="Programming" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst/>
@@ -18,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="52">
   <si>
     <t>Key</t>
   </si>
@@ -38,7 +39,7 @@
     <t>Instructions</t>
   </si>
   <si>
-    <t>请独立完成试卷。单项选择题和填空题自动判分，程序设计题需人工阅卷。</t>
+    <t>请独立完成试卷。单项选择题和判断题自动判分，程序设计题需人工阅卷。</t>
   </si>
   <si>
     <t>Enabled</t>
@@ -144,6 +145,24 @@
   </si>
   <si>
     <t>欧几里得</t>
+  </si>
+  <si>
+    <t>Enable</t>
+  </si>
+  <si>
+    <t>TF1</t>
+  </si>
+  <si>
+    <t>程序员用C、C++、Python、Scratch等编写的程序能在 CPU 上直接执行。</t>
+  </si>
+  <si>
+    <t>TF2</t>
+  </si>
+  <si>
+    <t>在C++语言中，标识符中可以有数字，但不能以数字开头。</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
   <si>
     <t>Description</t>
@@ -169,7 +188,7 @@
     <numFmt numFmtId="179" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="21">
+  <fonts count="47" x14ac:knownFonts="47">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -182,6 +201,124 @@
       <charset val="134"/>
       <b/>
       <i val="0"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="0"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18.0"/>
+      <color rgb="FF1F497D"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="15.0"/>
+      <color rgb="FF1F497D"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="13.0"/>
+      <color rgb="FF1F497D"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF1F497D"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12.0"/>
@@ -337,6 +474,27 @@
       <strike val="0"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -350,9 +508,54 @@
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="14.0"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="67">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -360,15 +563,15 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF163B75"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
@@ -554,8 +757,200 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2DCDB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEEF3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8CCE4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6B8B7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8E4BC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCC0DA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7DEE8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCD5B4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95B3D7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA9694"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D79B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1A0C7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92CDDC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFABF8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0504D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BBB59"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8064A2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BACC6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF79646"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF163B75"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="25">
     <border>
       <diagonal/>
     </border>
@@ -726,40 +1121,183 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF4F81BD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFA7BFDE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF95B3D7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF4F81BD"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF4F81BD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyAlignment="0" applyFont="0" applyBorder="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyAlignment="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="40" borderId="0" applyNumberFormat="0" applyAlignment="0" applyBorder="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="1" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyBorder="1" applyFill="1" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="5" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyBorder="1" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyBorder="1" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyBorder="1" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyBorder="1" applyFill="1" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0"/>
@@ -784,26 +1322,166 @@
     <xf numFmtId="0" fontId="18" fillId="32" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" xfId="0"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" xfId="0"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" xfId="0"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" xfId="0"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" applyBorder="1" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="13" applyBorder="1" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyBorder="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="14" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="15" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="17" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="18" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="19" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="21" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="23" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="42" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="43" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="44" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="45" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="46" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="47" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="48" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="49" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="50" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="51" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="52" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="53" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="54" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="55" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="56" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="57" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="58" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="59" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="60" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="61" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="62" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="63" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="64" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="65" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyBorder="1" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="13" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="66" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="66" borderId="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFill="1" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="66" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="66" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="66" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="66" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="66" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="66" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="66" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="66" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="66" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="66" borderId="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="66" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="18" applyBorder="1" xfId="3"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyFill="1" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="1" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="注释" xfId="1" builtinId="10"/>
+    <cellStyle name="差" xfId="2" builtinId="27"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1039,41 +1717,41 @@
     <outlinePr showOutlineSymbols="1"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="9.0" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" defaultColWidth="9.0" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="1"/>
     <col min="2" max="2" width="90.0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row ht="14.25" x14ac:dyDescent="0.15" r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+    <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="1" spans="1:2">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row ht="13.5" x14ac:dyDescent="0.15" r="2" spans="1:2">
-      <c r="A2" s="3" t="s">
+    <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="2" spans="1:2">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row ht="13.5" x14ac:dyDescent="0.15" r="3" spans="1:2">
-      <c r="A3" s="3" t="s">
+    <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="3" spans="1:2">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="139">
         <v>90</v>
       </c>
     </row>
-    <row ht="13.5" x14ac:dyDescent="0.15" r="4" spans="1:2">
-      <c r="A4" s="3" t="s">
+    <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="4" spans="1:2">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="138" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1095,129 +1773,129 @@
     <outlinePr showOutlineSymbols="1"/>
   </sheetPr>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="9.0" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" defaultColWidth="9.0" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="1"/>
     <col min="2" max="2" width="14.0" customWidth="1"/>
-    <col min="3" max="3" width="56.0" customWidth="1"/>
+    <col min="3" max="3" width="67.0" customWidth="1"/>
     <col min="4" max="7" width="24.0" customWidth="1"/>
     <col min="8" max="8" width="12.0" customWidth="1"/>
-    <col min="9" max="9" width="10.0" customWidth="1"/>
+    <col min="9" max="9" width="10.0" customWidth="1" style="113"/>
   </cols>
   <sheetData>
-    <row ht="14.25" x14ac:dyDescent="0.15" r="1" spans="1:9">
-      <c r="A1" s="2" t="s">
+    <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="1" spans="1:9">
+      <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="140" t="s">
         <v>14</v>
       </c>
     </row>
-    <row ht="13.5" x14ac:dyDescent="0.15" r="2" spans="1:9">
-      <c r="A2" s="3" t="s">
+    <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="2" spans="1:9">
+      <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="139">
         <v>5</v>
       </c>
     </row>
-    <row ht="13.5" x14ac:dyDescent="0.15" r="3" spans="1:9">
-      <c r="A3" s="3" t="s">
+    <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="3" spans="1:9">
+      <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="139">
         <v>5</v>
       </c>
     </row>
-    <row ht="13.5" x14ac:dyDescent="0.15" r="4" spans="1:9">
-      <c r="A4" s="3" t="s">
+    <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="4" spans="1:9">
+      <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="139">
         <v>5</v>
       </c>
     </row>
@@ -1239,63 +1917,63 @@
     <outlinePr showOutlineSymbols="1"/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="9.0" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" defaultColWidth="9.0" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="1"/>
     <col min="2" max="2" width="14.0" customWidth="1"/>
     <col min="3" max="3" width="62.0" customWidth="1"/>
     <col min="4" max="4" width="24.0" customWidth="1"/>
-    <col min="5" max="5" width="10.0" customWidth="1"/>
+    <col min="5" max="5" width="10.0" customWidth="1" style="113"/>
   </cols>
   <sheetData>
-    <row ht="14.25" x14ac:dyDescent="0.15" r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+    <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="140" t="s">
         <v>14</v>
       </c>
     </row>
-    <row ht="13.5" x14ac:dyDescent="0.15" r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+    <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="2" spans="1:5">
+      <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="139">
         <v>5</v>
       </c>
     </row>
-    <row ht="13.5" x14ac:dyDescent="0.15" r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
+    <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="139">
         <v>5</v>
       </c>
     </row>
@@ -1317,7 +1995,7 @@
     <outlinePr showOutlineSymbols="1"/>
   </sheetPr>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="9.0" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" defaultColWidth="9.0" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="1"/>
     <col min="2" max="2" width="14.0" customWidth="1"/>
@@ -1326,37 +2004,37 @@
     <col min="5" max="5" width="10.0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row ht="14.25" x14ac:dyDescent="0.15" r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+    <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row ht="13.5" x14ac:dyDescent="0.15" r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+    <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="2" spans="1:5">
+      <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="B2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="4">
         <v>20</v>
       </c>
     </row>
@@ -1370,4 +2048,77 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" defaultColWidth="8.0" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="2" width="9.375" customWidth="1"/>
+    <col min="3" max="3" width="72.375" customWidth="1"/>
+    <col min="4" max="5" width="9.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row s="135" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="1" spans="1:5">
+      <c r="A1" s="136" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="136" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="136" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="136" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="136" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="2" spans="1:5">
+      <c r="A2" s="114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="115" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="114" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="115" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="114">
+        <v>2</v>
+      </c>
+    </row>
+    <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="3" spans="1:5">
+      <c r="A3" s="114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="115" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="115" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="114" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="114">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="0" type="noConversion"/>
+  <pageMargins left="0.7006944633844331" right="0.7006944633844331" top="0.7520833822685903" bottom="0.7520833822685903" header="0.29930554506346935" footer="0.29930554506346935"/>
+  <pageSetup paperSize="9"/>
+  <extLst>
+    <ext uri="{2D9387EB-5337-4D45-933B-B4D357D02E09}">
+      <gutter val="0.0" pos="0"/>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/exams/noip_basic.xlsx
+++ b/exams/noip_basic.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="105" yWindow="108" windowWidth="30546" windowHeight="17473" activeTab="3" tabRatio="600"/>
+    <workbookView xWindow="90" yWindow="92" windowWidth="30531" windowHeight="17458" activeTab="0" tabRatio="600"/>
   </bookViews>
   <sheets>
     <sheet name="ExamConfig" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,52 @@
     <t>Title</t>
   </si>
   <si>
-    <t>摸底测试</t>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>GESP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>基础</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>测试</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>DurationMinutes</t>
@@ -188,7 +233,7 @@
     <numFmt numFmtId="179" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="47" x14ac:knownFonts="47">
+  <fonts count="46" x14ac:knownFonts="46">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -319,6 +364,63 @@
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="14.0"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
     </font>
     <font>
       <sz val="12.0"/>
@@ -474,27 +576,6 @@
       <strike val="0"/>
     </font>
     <font>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b/>
-      <i val="0"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b/>
-      <i val="0"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -508,54 +589,9 @@
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b/>
-      <i val="0"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b/>
-      <i val="0"/>
-    </font>
-    <font>
-      <sz val="14.0"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="14.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b/>
-      <i val="0"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="67">
+  <fills count="66">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -940,12 +976,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF79646"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF163B75"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1137,6 +1167,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1243,35 +1288,20 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyAlignment="0" applyFont="0" applyBorder="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyAlignment="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="0" applyAlignment="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="40" borderId="0" applyNumberFormat="0" applyAlignment="0" applyBorder="1" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyAlignment="0" applyBorder="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1334,146 +1364,139 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="13" applyBorder="1" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyBorder="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="1" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="1" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="1" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="1" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" applyBorder="1" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="1" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyBorder="1" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="14" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="15" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="17" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="18" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="41" borderId="19" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="21" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyBorder="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="15" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="16" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="23" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="42" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="43" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="44" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="45" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="46" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="47" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="48" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="49" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="50" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="51" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="52" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="53" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="54" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="55" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="56" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="57" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="58" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="59" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="60" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="61" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="62" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="63" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="64" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="65" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="17" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="38" borderId="18" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="40" borderId="19" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="20" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="21" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="22" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="23" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="24" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="42" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="43" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="44" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="45" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="46" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="47" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="48" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="49" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="50" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="51" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="52" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="53" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="54" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="55" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="56" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="57" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="58" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="59" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="60" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="61" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="62" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="63" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="64" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="65" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyFill="1" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="66" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="66" borderId="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="66" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="66" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="66" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="66" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="66" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="66" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="44" fillId="66" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="66" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="66" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="66" borderId="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="66" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="18" applyBorder="1" xfId="3"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyFill="1" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="1" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -1735,7 +1758,7 @@
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="135" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1743,7 +1766,7 @@
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="139">
+      <c r="B3" s="82">
         <v>90</v>
       </c>
     </row>
@@ -1751,7 +1774,7 @@
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="138" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1780,7 +1803,7 @@
     <col min="3" max="3" width="67.0" customWidth="1"/>
     <col min="4" max="7" width="24.0" customWidth="1"/>
     <col min="8" max="8" width="12.0" customWidth="1"/>
-    <col min="9" max="9" width="10.0" customWidth="1" style="113"/>
+    <col min="9" max="9" width="10.0" customWidth="1" style="88"/>
   </cols>
   <sheetData>
     <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="1" spans="1:9">
@@ -1808,7 +1831,7 @@
       <c r="H1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="140" t="s">
+      <c r="I1" s="83" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1837,7 +1860,7 @@
       <c r="H2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="139">
+      <c r="I2" s="82">
         <v>5</v>
       </c>
     </row>
@@ -1866,7 +1889,7 @@
       <c r="H3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="139">
+      <c r="I3" s="82">
         <v>5</v>
       </c>
     </row>
@@ -1895,7 +1918,7 @@
       <c r="H4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="139">
+      <c r="I4" s="82">
         <v>5</v>
       </c>
     </row>
@@ -1923,14 +1946,14 @@
     <col min="2" max="2" width="14.0" customWidth="1"/>
     <col min="3" max="3" width="62.0" customWidth="1"/>
     <col min="4" max="4" width="24.0" customWidth="1"/>
-    <col min="5" max="5" width="10.0" customWidth="1" style="113"/>
+    <col min="5" max="5" width="10.0" customWidth="1" style="88"/>
   </cols>
   <sheetData>
     <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="106" t="s">
+      <c r="B1" s="58" t="s">
         <v>8</v>
       </c>
       <c r="C1" s="3" t="s">
@@ -1939,7 +1962,7 @@
       <c r="D1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="140" t="s">
+      <c r="E1" s="83" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1956,7 +1979,7 @@
       <c r="D2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="139">
+      <c r="E2" s="82">
         <v>5</v>
       </c>
     </row>
@@ -1973,7 +1996,7 @@
       <c r="D3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="139">
+      <c r="E3" s="82">
         <v>5</v>
       </c>
     </row>
@@ -2052,6 +2075,9 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr showOutlineSymbols="1"/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1" defaultColWidth="8.0" x14ac:dyDescent="0.15"/>
   <cols>
@@ -2060,54 +2086,54 @@
     <col min="4" max="5" width="9.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row s="135" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="1" spans="1:5">
-      <c r="A1" s="136" t="s">
+    <row s="64" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="1" spans="1:5">
+      <c r="A1" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="136" t="s">
+      <c r="B1" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="136" t="s">
+      <c r="C1" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="136" t="s">
+      <c r="D1" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="136" t="s">
+      <c r="E1" s="71" t="s">
         <v>14</v>
       </c>
     </row>
     <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="2" spans="1:5">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="115" t="s">
+      <c r="B2" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="114" t="s">
+      <c r="C2" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="115" t="s">
+      <c r="D2" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="114">
+      <c r="E2" s="64">
         <v>2</v>
       </c>
     </row>
     <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="3" spans="1:5">
-      <c r="A3" s="114" t="s">
+      <c r="A3" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="115" t="s">
+      <c r="B3" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="115" t="s">
+      <c r="C3" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="114" t="s">
+      <c r="D3" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="114">
+      <c r="E3" s="64">
         <v>2</v>
       </c>
     </row>

--- a/exams/noip_basic.xlsx
+++ b/exams/noip_basic.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="92" windowWidth="30531" windowHeight="17458" activeTab="0" tabRatio="600"/>
+    <workbookView xWindow="75" yWindow="77" windowWidth="30516" windowHeight="17443" activeTab="3" tabRatio="600"/>
   </bookViews>
   <sheets>
     <sheet name="ExamConfig" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="53">
   <si>
     <t>Key</t>
   </si>
@@ -201,13 +201,16 @@
     <t>程序员用C、C++、Python、Scratch等编写的程序能在 CPU 上直接执行。</t>
   </si>
   <si>
+    <t>T</t>
+  </si>
+  <si>
     <t>TF2</t>
   </si>
   <si>
     <t>在C++语言中，标识符中可以有数字，但不能以数字开头。</t>
   </si>
   <si>
-    <t>N</t>
+    <t>F</t>
   </si>
   <si>
     <t>Description</t>
@@ -1301,7 +1304,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1436,6 +1439,12 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyBorder="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyBorder="1" xfId="0">
       <alignment vertical="center"/>
@@ -1496,7 +1505,7 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyFill="1" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -1758,7 +1767,7 @@
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1803,7 +1812,7 @@
     <col min="3" max="3" width="67.0" customWidth="1"/>
     <col min="4" max="7" width="24.0" customWidth="1"/>
     <col min="8" max="8" width="12.0" customWidth="1"/>
-    <col min="9" max="9" width="10.0" customWidth="1" style="88"/>
+    <col min="9" max="9" width="10.0" customWidth="1" style="90"/>
   </cols>
   <sheetData>
     <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="1" spans="1:9">
@@ -1946,7 +1955,7 @@
     <col min="2" max="2" width="14.0" customWidth="1"/>
     <col min="3" max="3" width="62.0" customWidth="1"/>
     <col min="4" max="4" width="24.0" customWidth="1"/>
-    <col min="5" max="5" width="10.0" customWidth="1" style="88"/>
+    <col min="5" max="5" width="10.0" customWidth="1" style="90"/>
   </cols>
   <sheetData>
     <row ht="16.5" customHeight="1" x14ac:dyDescent="0.15" r="1" spans="1:5">
@@ -2038,7 +2047,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>14</v>
@@ -2049,13 +2058,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E2" s="4">
         <v>20</v>
@@ -2114,7 +2123,7 @@
         <v>44</v>
       </c>
       <c r="D2" s="64" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E2" s="64">
         <v>2</v>
@@ -2125,13 +2134,13 @@
         <v>15</v>
       </c>
       <c r="B3" s="64" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="64" t="s">
         <v>47</v>
+      </c>
+      <c r="D3" s="137" t="s">
+        <v>48</v>
       </c>
       <c r="E3" s="64">
         <v>2</v>
